--- a/data/Jugadores/Vegueta.xlsx
+++ b/data/Jugadores/Vegueta.xlsx
@@ -394,10 +394,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -405,10 +405,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
         <v>2</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
